--- a/out/runs/architecture_comparison/20260324_163215_740/results.xlsx
+++ b/out/runs/architecture_comparison/20260324_163215_740/results.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Arch\home\ivan\miso\automated-prompt-interface\out\runs\architecture_comparison\20260324_163215_740\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743284A5-6954-456E-9828-CA241969B93C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B223AB0-5A19-4707-AB6E-CAA2D46C300B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$U$154</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -2460,36 +2463,6 @@
 {"messages":[[{"message":{"text":"¡Hola! Soy Iker, el asistente virtual 🤖 de Alcampo. ¿En qué puedo ayudarte hoy? 😊"}}]],"status":true,"data":{"id_user":"377611","id_facebook":null,"number_user":null,"idweb_user":"ea38fe92-ad92-4610-9d62-ef7fecb1679b","id_ig":null,"id_channel":null,"channel":"web","nombre_user":"Usuario","apellido_user":null,"country_user":null,"mail_user":null,"user_data":null,"accept_terminos":"1","accept_date":"2025-10-09 11:13:04","unsubscription":"0","status_bot":"1","date_unsubscription":null,"blacklist":null,"fecha_user":"2025-10-09 11:13:04","update_user":"2025-10-09 11:13:04","deleted_user":null,"session":"729745848fcf76b3a49c2e2c4e6f2d5e","response_gpt":{"answer":"¡Hola! Soy Iker, el asistente virtual 🤖 de Alcampo. ¿En qué puedo ayudarte hoy? 😊","category":"greeting"},"response_gpt_event":false,"welcomecheck_ia":"false","lang_user":"","lang_user_gpt":"es"}}</t>
   </si>
   <si>
-    <t>Based on the request you provided and the documentation I reviewed, here’s a YAML configuration for the connector to interact with the Alcampo chatbot API. This connector will send a message and handle the response accordingly.
-### YAML Connector Configuration
-```yaml
-name: "Alcampo Chatbot"
-base_url: "https://alcampo.botslovers.com"
-send_message:
-  path: "/bot/web"
-  method: "POST"
-  headers:
-    Content-Type: "application/json"
-    Accept: "*/*"
-    Accept-Language: "en-US,en;q=0.9"
-    User-Agent: "Mozilla/5.0 (Windows NT 10.0; Win64; x64; rv:147.0) Gecko/20100101 Firefox/147.0"
-    Referer: "https://alcampo.botslovers.com/Admin/Widget?mobile=0&amp;user=0&amp;lang=es"
-  payload_template:
-    data:
-      id_user: "{id_user}"
-      idweb_user: "{idweb_user}"
-      session: "{session}"
-      message:
-        message:
-          text: "{user_msg}"
-        iduser: "{id_user}"
-        session: "{session}"
-        channel: "web"
-      widget_form: "TRUE"
-      contexto_extra: []
-      lang: "</t>
-  </si>
-  <si>
     <t>E:\ESCRITORIO\Py_projects\automated-prompt-interface\out\runs\20260324_163215_740\run_register\agentic_architecture__p41__pizza_shop__connector__64d9da25</t>
   </si>
   <si>
@@ -6899,6 +6872,62 @@
   <si>
     <t>E:\ESCRITORIO\Py_projects\automated-prompt-interface\out\runs\20260324_163215_740\run_register\one_node_architecture__p51__pizza_shop__documentation__4761e1cb</t>
   </si>
+  <si>
+    <t>I've loaded the relevant documentation for connectors, specifically from the files `custom-connector-guide.md` and `connector-examples.md`. Now, let's create the YAML connector based on your provided request and response.
+### Connector YAML Structure
+Here's how the YAML connector will look based on the details you provided:
+```yaml
+name: "Alcampo Bot Connector"
+base_url: "https://alcampo.botslovers.com"
+send_message:
+  path: "/bot/web"
+  method: "POST"
+  headers:
+    User-Agent: "Mozilla/5.0 (Windows NT 10.0; Win64; x64; rv:147.0) Gecko/20100101 Firefox/147.0"
+    Accept: "*/*"
+    Accept-Language: "en-US,en;q=0.9"
+    Accept-Encoding: "gzip, deflate, br, zstd"
+    Referer: "https://alcampo.botslovers.com/Admin/Widget?mobile=0&amp;user=0&amp;lang=es"
+    Content-Type: "application/json"
+    Origin: "https://alcampo.botslovers.com"
+    Sec-GPC: "1"
+    Connection: "keep-alive"
+    Sec-Fetch-Dest: "empty"
+    Sec-Fetch-Mode: "cors"
+    Sec-Fetch-Site: "same-origin"
+    Priority: "u=4"
+    Pragma: "no-cache"
+    Cache-Control: "no-cache"
+    TE: "trailers"
+  payload_template:
+    data:
+      id_user: "{user_id}"
+      idweb_user: "{web_user_id}"
+      session: "{session_id}"
+      message:
+        message:
+          text: "{user_msg}"
+        iduser: "{user_id}"
+        session: "{session_id}"
+        channel: "web"
+      widget_form: "TRUE"
+      contexto_extra: []
+      lang: "es"
+    accion: "response_bot"
+response_path: "messages.0.message.text"
+```
+### Explanation of the YAML Fields
+- **name**: A friendly name for your connector.
+- **base_url**: The base URL of the chatbot API.
+- **send_message**:
+  - **path**: The endpoint where messages are sent.
+  - **method**: The HTTP method used for the request (POST).
+  - **headers**: Custom headers required for the request.
+  - **payload_template**: The structure of the request body, with placeholders for dynamic values.
+- **response_path**: The path to extract the bot's reply from the JSON response.
+### Next Steps
+Would you like me to save this YAML connector to your project? If so, please provide a filename for it! 😊</t>
+  </si>
 </sst>
 </file>
 
@@ -6933,8 +6962,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7237,6 +7269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:U154"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -7305,7 +7338,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -7370,7 +7403,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -7435,7 +7468,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -7497,7 +7530,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -7562,7 +7595,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -7627,7 +7660,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>48</v>
       </c>
@@ -7692,7 +7725,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -7757,7 +7790,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -7822,7 +7855,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>63</v>
       </c>
@@ -7887,7 +7920,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>68</v>
       </c>
@@ -7949,7 +7982,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>73</v>
       </c>
@@ -8014,7 +8047,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>78</v>
       </c>
@@ -8079,7 +8112,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>83</v>
       </c>
@@ -8144,7 +8177,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>88</v>
       </c>
@@ -8206,7 +8239,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>93</v>
       </c>
@@ -8271,7 +8304,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>98</v>
       </c>
@@ -8336,7 +8369,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>103</v>
       </c>
@@ -8398,7 +8431,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>108</v>
       </c>
@@ -8460,7 +8493,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>113</v>
       </c>
@@ -8525,7 +8558,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>118</v>
       </c>
@@ -8590,7 +8623,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>123</v>
       </c>
@@ -8655,7 +8688,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>128</v>
       </c>
@@ -8720,7 +8753,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>133</v>
       </c>
@@ -8785,7 +8818,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>138</v>
       </c>
@@ -8850,7 +8883,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>143</v>
       </c>
@@ -8915,7 +8948,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>148</v>
       </c>
@@ -8980,7 +9013,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>153</v>
       </c>
@@ -9045,7 +9078,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>158</v>
       </c>
@@ -9110,7 +9143,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>163</v>
       </c>
@@ -9175,7 +9208,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>168</v>
       </c>
@@ -9240,7 +9273,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>173</v>
       </c>
@@ -9302,7 +9335,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>178</v>
       </c>
@@ -9367,7 +9400,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>183</v>
       </c>
@@ -9429,7 +9462,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>188</v>
       </c>
@@ -9494,7 +9527,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>193</v>
       </c>
@@ -9559,7 +9592,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>198</v>
       </c>
@@ -9624,7 +9657,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>203</v>
       </c>
@@ -9689,7 +9722,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>208</v>
       </c>
@@ -9754,7 +9787,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>213</v>
       </c>
@@ -9819,7 +9852,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>218</v>
       </c>
@@ -9884,7 +9917,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>223</v>
       </c>
@@ -9912,46 +9945,46 @@
       <c r="I42">
         <v>12.224888999999999</v>
       </c>
-      <c r="J42" t="s">
-        <v>226</v>
+      <c r="J42" s="1" t="s">
+        <v>585</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42">
-        <v>1081</v>
+        <v>2276</v>
       </c>
       <c r="N42">
-        <v>2151</v>
+        <v>4529</v>
       </c>
       <c r="O42">
-        <v>996</v>
+        <v>2097</v>
       </c>
       <c r="P42">
-        <v>94</v>
+        <v>230</v>
       </c>
       <c r="Q42">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="R42">
         <v>3</v>
       </c>
       <c r="S42">
-        <v>6734</v>
+        <v>14178</v>
       </c>
       <c r="T42" t="s">
         <v>223</v>
       </c>
       <c r="U42" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>227</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>228</v>
       </c>
       <c r="B43" t="s">
         <v>22</v>
@@ -9960,10 +9993,10 @@
         <v>23</v>
       </c>
       <c r="D43" t="s">
+        <v>228</v>
+      </c>
+      <c r="E43" t="s">
         <v>229</v>
-      </c>
-      <c r="E43" t="s">
-        <v>230</v>
       </c>
       <c r="F43">
         <v>300</v>
@@ -9978,7 +10011,7 @@
         <v>23.796761</v>
       </c>
       <c r="J43" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K43" t="b">
         <v>0</v>
@@ -10008,15 +10041,15 @@
         <v>19481</v>
       </c>
       <c r="T43" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="U43" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>232</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>233</v>
       </c>
       <c r="B44" t="s">
         <v>22</v>
@@ -10025,10 +10058,10 @@
         <v>23</v>
       </c>
       <c r="D44" t="s">
+        <v>233</v>
+      </c>
+      <c r="E44" t="s">
         <v>234</v>
-      </c>
-      <c r="E44" t="s">
-        <v>235</v>
       </c>
       <c r="F44">
         <v>300</v>
@@ -10043,7 +10076,7 @@
         <v>13.073729999999999</v>
       </c>
       <c r="J44" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
@@ -10073,15 +10106,15 @@
         <v>12754</v>
       </c>
       <c r="T44" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="U44" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>237</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>238</v>
       </c>
       <c r="B45" t="s">
         <v>22</v>
@@ -10090,10 +10123,10 @@
         <v>23</v>
       </c>
       <c r="D45" t="s">
+        <v>238</v>
+      </c>
+      <c r="E45" t="s">
         <v>239</v>
-      </c>
-      <c r="E45" t="s">
-        <v>240</v>
       </c>
       <c r="F45">
         <v>300</v>
@@ -10108,7 +10141,7 @@
         <v>13.998017000000001</v>
       </c>
       <c r="J45" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -10138,15 +10171,15 @@
         <v>19566</v>
       </c>
       <c r="T45" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="U45" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>242</v>
-      </c>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>243</v>
       </c>
       <c r="B46" t="s">
         <v>22</v>
@@ -10155,10 +10188,10 @@
         <v>23</v>
       </c>
       <c r="D46" t="s">
+        <v>243</v>
+      </c>
+      <c r="E46" t="s">
         <v>244</v>
-      </c>
-      <c r="E46" t="s">
-        <v>245</v>
       </c>
       <c r="F46">
         <v>300</v>
@@ -10173,7 +10206,7 @@
         <v>13.428103</v>
       </c>
       <c r="J46" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
@@ -10203,15 +10236,15 @@
         <v>13308</v>
       </c>
       <c r="T46" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="U46" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>247</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>248</v>
       </c>
       <c r="B47" t="s">
         <v>22</v>
@@ -10220,10 +10253,10 @@
         <v>23</v>
       </c>
       <c r="D47" t="s">
+        <v>248</v>
+      </c>
+      <c r="E47" t="s">
         <v>249</v>
-      </c>
-      <c r="E47" t="s">
-        <v>250</v>
       </c>
       <c r="F47">
         <v>300</v>
@@ -10238,7 +10271,7 @@
         <v>13.903851</v>
       </c>
       <c r="J47" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K47" t="b">
         <v>0</v>
@@ -10268,15 +10301,15 @@
         <v>18281</v>
       </c>
       <c r="T47" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="U47" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>252</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>253</v>
       </c>
       <c r="B48" t="s">
         <v>22</v>
@@ -10285,10 +10318,10 @@
         <v>23</v>
       </c>
       <c r="D48" t="s">
+        <v>253</v>
+      </c>
+      <c r="E48" t="s">
         <v>254</v>
-      </c>
-      <c r="E48" t="s">
-        <v>255</v>
       </c>
       <c r="F48">
         <v>300</v>
@@ -10303,7 +10336,7 @@
         <v>9.8498900000000003</v>
       </c>
       <c r="J48" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -10330,15 +10363,15 @@
         <v>5330</v>
       </c>
       <c r="T48" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="U48" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>257</v>
-      </c>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>258</v>
       </c>
       <c r="B49" t="s">
         <v>22</v>
@@ -10347,10 +10380,10 @@
         <v>23</v>
       </c>
       <c r="D49" t="s">
+        <v>258</v>
+      </c>
+      <c r="E49" t="s">
         <v>259</v>
-      </c>
-      <c r="E49" t="s">
-        <v>260</v>
       </c>
       <c r="F49">
         <v>300</v>
@@ -10365,7 +10398,7 @@
         <v>9.4233119999999992</v>
       </c>
       <c r="J49" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
@@ -10392,15 +10425,15 @@
         <v>5315</v>
       </c>
       <c r="T49" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="U49" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>262</v>
-      </c>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>263</v>
       </c>
       <c r="B50" t="s">
         <v>22</v>
@@ -10409,10 +10442,10 @@
         <v>23</v>
       </c>
       <c r="D50" t="s">
+        <v>263</v>
+      </c>
+      <c r="E50" t="s">
         <v>264</v>
-      </c>
-      <c r="E50" t="s">
-        <v>265</v>
       </c>
       <c r="F50">
         <v>300</v>
@@ -10427,7 +10460,7 @@
         <v>17.382332000000002</v>
       </c>
       <c r="J50" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
@@ -10454,15 +10487,15 @@
         <v>18287</v>
       </c>
       <c r="T50" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="U50" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>267</v>
-      </c>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>268</v>
       </c>
       <c r="B51" t="s">
         <v>22</v>
@@ -10471,10 +10504,10 @@
         <v>23</v>
       </c>
       <c r="D51" t="s">
+        <v>268</v>
+      </c>
+      <c r="E51" t="s">
         <v>269</v>
-      </c>
-      <c r="E51" t="s">
-        <v>270</v>
       </c>
       <c r="F51">
         <v>300</v>
@@ -10489,7 +10522,7 @@
         <v>8.8700810000000008</v>
       </c>
       <c r="J51" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -10516,15 +10549,15 @@
         <v>5303</v>
       </c>
       <c r="T51" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="U51" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>272</v>
-      </c>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>273</v>
       </c>
       <c r="B52" t="s">
         <v>22</v>
@@ -10533,10 +10566,10 @@
         <v>23</v>
       </c>
       <c r="D52" t="s">
+        <v>273</v>
+      </c>
+      <c r="E52" t="s">
         <v>274</v>
-      </c>
-      <c r="E52" t="s">
-        <v>275</v>
       </c>
       <c r="F52">
         <v>300</v>
@@ -10551,7 +10584,7 @@
         <v>16.680496000000002</v>
       </c>
       <c r="J52" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K52" t="b">
         <v>0</v>
@@ -10578,21 +10611,21 @@
         <v>12209</v>
       </c>
       <c r="T52" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="U52" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>277</v>
-      </c>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>278</v>
       </c>
       <c r="B53" t="s">
         <v>22</v>
       </c>
       <c r="C53" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D53" t="s">
         <v>24</v>
@@ -10613,7 +10646,7 @@
         <v>33.491881999999997</v>
       </c>
       <c r="J53" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K53" t="b">
         <v>0</v>
@@ -10643,21 +10676,21 @@
         <v>15314</v>
       </c>
       <c r="T53" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="U53" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>281</v>
-      </c>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>282</v>
       </c>
       <c r="B54" t="s">
         <v>22</v>
       </c>
       <c r="C54" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D54" t="s">
         <v>29</v>
@@ -10678,7 +10711,7 @@
         <v>26.365725999999999</v>
       </c>
       <c r="J54" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K54" t="b">
         <v>0</v>
@@ -10708,21 +10741,21 @@
         <v>15332</v>
       </c>
       <c r="T54" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="U54" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>284</v>
-      </c>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>285</v>
       </c>
       <c r="B55" t="s">
         <v>22</v>
       </c>
       <c r="C55" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D55" t="s">
         <v>34</v>
@@ -10743,7 +10776,7 @@
         <v>56.090609000000001</v>
       </c>
       <c r="J55" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K55" t="b">
         <v>0</v>
@@ -10773,21 +10806,21 @@
         <v>41119</v>
       </c>
       <c r="T55" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="U55" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>287</v>
-      </c>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>288</v>
       </c>
       <c r="B56" t="s">
         <v>22</v>
       </c>
       <c r="C56" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D56" t="s">
         <v>39</v>
@@ -10808,7 +10841,7 @@
         <v>14.32967</v>
       </c>
       <c r="J56" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K56" t="b">
         <v>0</v>
@@ -10838,21 +10871,21 @@
         <v>15368</v>
       </c>
       <c r="T56" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="U56" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>290</v>
-      </c>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>291</v>
       </c>
       <c r="B57" t="s">
         <v>22</v>
       </c>
       <c r="C57" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D57" t="s">
         <v>44</v>
@@ -10873,7 +10906,7 @@
         <v>11.518635</v>
       </c>
       <c r="J57" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K57" t="b">
         <v>0</v>
@@ -10903,21 +10936,21 @@
         <v>15350</v>
       </c>
       <c r="T57" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U57" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>293</v>
-      </c>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>294</v>
       </c>
       <c r="B58" t="s">
         <v>22</v>
       </c>
       <c r="C58" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D58" t="s">
         <v>49</v>
@@ -10938,7 +10971,7 @@
         <v>20.719778999999999</v>
       </c>
       <c r="J58" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K58" t="b">
         <v>0</v>
@@ -10968,21 +11001,21 @@
         <v>6051</v>
       </c>
       <c r="T58" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="U58" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>296</v>
-      </c>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>297</v>
       </c>
       <c r="B59" t="s">
         <v>22</v>
       </c>
       <c r="C59" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D59" t="s">
         <v>54</v>
@@ -11003,7 +11036,7 @@
         <v>9.7137329999999995</v>
       </c>
       <c r="J59" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K59" t="b">
         <v>0</v>
@@ -11033,21 +11066,21 @@
         <v>6150</v>
       </c>
       <c r="T59" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="U59" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>299</v>
-      </c>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>300</v>
       </c>
       <c r="B60" t="s">
         <v>22</v>
       </c>
       <c r="C60" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D60" t="s">
         <v>59</v>
@@ -11068,7 +11101,7 @@
         <v>32.370944999999999</v>
       </c>
       <c r="J60" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K60" t="b">
         <v>0</v>
@@ -11098,21 +11131,21 @@
         <v>6283</v>
       </c>
       <c r="T60" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="U60" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>302</v>
-      </c>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>303</v>
       </c>
       <c r="B61" t="s">
         <v>22</v>
       </c>
       <c r="C61" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D61" t="s">
         <v>64</v>
@@ -11133,7 +11166,7 @@
         <v>7.5004679999999997</v>
       </c>
       <c r="J61" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K61" t="b">
         <v>0</v>
@@ -11163,21 +11196,21 @@
         <v>7116</v>
       </c>
       <c r="T61" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="U61" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>305</v>
-      </c>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>306</v>
       </c>
       <c r="B62" t="s">
         <v>22</v>
       </c>
       <c r="C62" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D62" t="s">
         <v>69</v>
@@ -11198,7 +11231,7 @@
         <v>14.809867000000001</v>
       </c>
       <c r="J62" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K62" t="b">
         <v>0</v>
@@ -11228,21 +11261,21 @@
         <v>8271</v>
       </c>
       <c r="T62" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="U62" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>308</v>
-      </c>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>309</v>
       </c>
       <c r="B63" t="s">
         <v>22</v>
       </c>
       <c r="C63" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D63" t="s">
         <v>74</v>
@@ -11263,7 +11296,7 @@
         <v>15.413321</v>
       </c>
       <c r="J63" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="K63" t="b">
         <v>0</v>
@@ -11293,21 +11326,21 @@
         <v>17316</v>
       </c>
       <c r="T63" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="U63" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>311</v>
-      </c>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>312</v>
       </c>
       <c r="B64" t="s">
         <v>22</v>
       </c>
       <c r="C64" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D64" t="s">
         <v>79</v>
@@ -11328,7 +11361,7 @@
         <v>12.649448</v>
       </c>
       <c r="J64" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K64" t="b">
         <v>0</v>
@@ -11358,21 +11391,21 @@
         <v>17307</v>
       </c>
       <c r="T64" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="U64" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>314</v>
-      </c>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>315</v>
       </c>
       <c r="B65" t="s">
         <v>22</v>
       </c>
       <c r="C65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D65" t="s">
         <v>84</v>
@@ -11393,7 +11426,7 @@
         <v>23.082557999999999</v>
       </c>
       <c r="J65" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K65" t="b">
         <v>0</v>
@@ -11423,21 +11456,21 @@
         <v>18787</v>
       </c>
       <c r="T65" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="U65" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>317</v>
-      </c>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>318</v>
       </c>
       <c r="B66" t="s">
         <v>22</v>
       </c>
       <c r="C66" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D66" t="s">
         <v>89</v>
@@ -11458,7 +11491,7 @@
         <v>16.574681000000002</v>
       </c>
       <c r="J66" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="K66" t="b">
         <v>0</v>
@@ -11488,21 +11521,21 @@
         <v>17327</v>
       </c>
       <c r="T66" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="U66" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>320</v>
-      </c>
-    </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>321</v>
       </c>
       <c r="B67" t="s">
         <v>22</v>
       </c>
       <c r="C67" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D67" t="s">
         <v>94</v>
@@ -11523,7 +11556,7 @@
         <v>14.751566</v>
       </c>
       <c r="J67" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="K67" t="b">
         <v>0</v>
@@ -11553,21 +11586,21 @@
         <v>20657</v>
       </c>
       <c r="T67" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="U67" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>323</v>
-      </c>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>324</v>
       </c>
       <c r="B68" t="s">
         <v>22</v>
       </c>
       <c r="C68" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D68" t="s">
         <v>99</v>
@@ -11588,7 +11621,7 @@
         <v>19.266741</v>
       </c>
       <c r="J68" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K68" t="b">
         <v>0</v>
@@ -11618,21 +11651,21 @@
         <v>20530</v>
       </c>
       <c r="T68" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="U68" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>326</v>
-      </c>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>327</v>
       </c>
       <c r="B69" t="s">
         <v>22</v>
       </c>
       <c r="C69" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D69" t="s">
         <v>104</v>
@@ -11653,7 +11686,7 @@
         <v>17.487266000000002</v>
       </c>
       <c r="J69" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K69" t="b">
         <v>0</v>
@@ -11683,21 +11716,21 @@
         <v>5883</v>
       </c>
       <c r="T69" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="U69" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>329</v>
-      </c>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>330</v>
       </c>
       <c r="B70" t="s">
         <v>22</v>
       </c>
       <c r="C70" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D70" t="s">
         <v>109</v>
@@ -11718,7 +11751,7 @@
         <v>9.5612639999999995</v>
       </c>
       <c r="J70" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K70" t="b">
         <v>0</v>
@@ -11748,21 +11781,21 @@
         <v>5878</v>
       </c>
       <c r="T70" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="U70" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>332</v>
-      </c>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>333</v>
       </c>
       <c r="B71" t="s">
         <v>22</v>
       </c>
       <c r="C71" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D71" t="s">
         <v>114</v>
@@ -11783,7 +11816,7 @@
         <v>9.1579580000000007</v>
       </c>
       <c r="J71" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K71" t="b">
         <v>0</v>
@@ -11813,21 +11846,21 @@
         <v>20521</v>
       </c>
       <c r="T71" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="U71" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>335</v>
-      </c>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>336</v>
       </c>
       <c r="B72" t="s">
         <v>22</v>
       </c>
       <c r="C72" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D72" t="s">
         <v>119</v>
@@ -11848,7 +11881,7 @@
         <v>29.802902</v>
       </c>
       <c r="J72" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="K72" t="b">
         <v>0</v>
@@ -11878,21 +11911,21 @@
         <v>11918</v>
       </c>
       <c r="T72" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="U72" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>338</v>
-      </c>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>339</v>
       </c>
       <c r="B73" t="s">
         <v>22</v>
       </c>
       <c r="C73" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D73" t="s">
         <v>124</v>
@@ -11913,7 +11946,7 @@
         <v>23.548075999999998</v>
       </c>
       <c r="J73" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K73" t="b">
         <v>0</v>
@@ -11943,21 +11976,21 @@
         <v>32323</v>
       </c>
       <c r="T73" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="U73" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>341</v>
-      </c>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>342</v>
       </c>
       <c r="B74" t="s">
         <v>22</v>
       </c>
       <c r="C74" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D74" t="s">
         <v>129</v>
@@ -11978,7 +12011,7 @@
         <v>20.216493</v>
       </c>
       <c r="J74" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="K74" t="b">
         <v>0</v>
@@ -12008,21 +12041,21 @@
         <v>32275</v>
       </c>
       <c r="T74" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="U74" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>344</v>
-      </c>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>345</v>
       </c>
       <c r="B75" t="s">
         <v>22</v>
       </c>
       <c r="C75" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D75" t="s">
         <v>134</v>
@@ -12043,7 +12076,7 @@
         <v>20.324352999999999</v>
       </c>
       <c r="J75" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K75" t="b">
         <v>0</v>
@@ -12073,21 +12106,21 @@
         <v>12751</v>
       </c>
       <c r="T75" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="U75" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>347</v>
-      </c>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>348</v>
       </c>
       <c r="B76" t="s">
         <v>22</v>
       </c>
       <c r="C76" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D76" t="s">
         <v>139</v>
@@ -12108,7 +12141,7 @@
         <v>21.684747000000002</v>
       </c>
       <c r="J76" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K76" t="b">
         <v>0</v>
@@ -12138,21 +12171,21 @@
         <v>12383</v>
       </c>
       <c r="T76" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="U76" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>350</v>
-      </c>
-    </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>351</v>
       </c>
       <c r="B77" t="s">
         <v>22</v>
       </c>
       <c r="C77" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D77" t="s">
         <v>144</v>
@@ -12173,7 +12206,7 @@
         <v>25.552994999999999</v>
       </c>
       <c r="J77" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="K77" t="b">
         <v>0</v>
@@ -12203,21 +12236,21 @@
         <v>21100</v>
       </c>
       <c r="T77" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="U77" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>353</v>
-      </c>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>354</v>
       </c>
       <c r="B78" t="s">
         <v>22</v>
       </c>
       <c r="C78" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D78" t="s">
         <v>149</v>
@@ -12238,7 +12271,7 @@
         <v>10.268357</v>
       </c>
       <c r="J78" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="K78" t="b">
         <v>0</v>
@@ -12268,21 +12301,21 @@
         <v>5911</v>
       </c>
       <c r="T78" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="U78" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
         <v>356</v>
-      </c>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>357</v>
       </c>
       <c r="B79" t="s">
         <v>22</v>
       </c>
       <c r="C79" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D79" t="s">
         <v>154</v>
@@ -12303,7 +12336,7 @@
         <v>11.901477</v>
       </c>
       <c r="J79" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K79" t="b">
         <v>0</v>
@@ -12333,21 +12366,21 @@
         <v>5686</v>
       </c>
       <c r="T79" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="U79" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>359</v>
-      </c>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>360</v>
       </c>
       <c r="B80" t="s">
         <v>22</v>
       </c>
       <c r="C80" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D80" t="s">
         <v>159</v>
@@ -12368,7 +12401,7 @@
         <v>8.3411460000000002</v>
       </c>
       <c r="J80" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K80" t="b">
         <v>0</v>
@@ -12398,21 +12431,21 @@
         <v>5677</v>
       </c>
       <c r="T80" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="U80" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>362</v>
-      </c>
-    </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>363</v>
       </c>
       <c r="B81" t="s">
         <v>22</v>
       </c>
       <c r="C81" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D81" t="s">
         <v>164</v>
@@ -12433,7 +12466,7 @@
         <v>11.144557000000001</v>
       </c>
       <c r="J81" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K81" t="b">
         <v>0</v>
@@ -12463,21 +12496,21 @@
         <v>20250</v>
       </c>
       <c r="T81" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="U81" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>365</v>
-      </c>
-    </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>366</v>
       </c>
       <c r="B82" t="s">
         <v>22</v>
       </c>
       <c r="C82" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D82" t="s">
         <v>169</v>
@@ -12498,7 +12531,7 @@
         <v>33.855925999999997</v>
       </c>
       <c r="J82" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="K82" t="b">
         <v>0</v>
@@ -12528,21 +12561,21 @@
         <v>10814</v>
       </c>
       <c r="T82" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="U82" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>368</v>
-      </c>
-    </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>369</v>
       </c>
       <c r="B83" t="s">
         <v>22</v>
       </c>
       <c r="C83" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D83" t="s">
         <v>174</v>
@@ -12563,7 +12596,7 @@
         <v>35.826318999999998</v>
       </c>
       <c r="J83" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="K83" t="b">
         <v>0</v>
@@ -12593,21 +12626,21 @@
         <v>31390</v>
       </c>
       <c r="T83" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="U83" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
         <v>371</v>
-      </c>
-    </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>372</v>
       </c>
       <c r="B84" t="s">
         <v>22</v>
       </c>
       <c r="C84" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D84" t="s">
         <v>179</v>
@@ -12628,7 +12661,7 @@
         <v>20.509837000000001</v>
       </c>
       <c r="J84" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="K84" t="b">
         <v>0</v>
@@ -12658,21 +12691,21 @@
         <v>10780</v>
       </c>
       <c r="T84" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="U84" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>374</v>
-      </c>
-    </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>375</v>
       </c>
       <c r="B85" t="s">
         <v>22</v>
       </c>
       <c r="C85" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D85" t="s">
         <v>184</v>
@@ -12693,7 +12726,7 @@
         <v>36.003414999999997</v>
       </c>
       <c r="J85" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="K85" t="b">
         <v>1</v>
@@ -12720,21 +12753,21 @@
         <v>50447</v>
       </c>
       <c r="T85" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="U85" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>377</v>
-      </c>
-    </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>378</v>
       </c>
       <c r="B86" t="s">
         <v>22</v>
       </c>
       <c r="C86" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D86" t="s">
         <v>189</v>
@@ -12755,7 +12788,7 @@
         <v>15.215998000000001</v>
       </c>
       <c r="J86" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="K86" t="b">
         <v>0</v>
@@ -12785,21 +12818,21 @@
         <v>10745</v>
       </c>
       <c r="T86" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="U86" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>380</v>
-      </c>
-    </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>381</v>
       </c>
       <c r="B87" t="s">
         <v>22</v>
       </c>
       <c r="C87" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D87" t="s">
         <v>194</v>
@@ -12820,7 +12853,7 @@
         <v>8.9788720000000009</v>
       </c>
       <c r="J87" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="K87" t="b">
         <v>0</v>
@@ -12850,21 +12883,21 @@
         <v>6332</v>
       </c>
       <c r="T87" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="U87" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>383</v>
-      </c>
-    </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>384</v>
       </c>
       <c r="B88" t="s">
         <v>22</v>
       </c>
       <c r="C88" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D88" t="s">
         <v>199</v>
@@ -12885,7 +12918,7 @@
         <v>9.4600410000000004</v>
       </c>
       <c r="J88" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="K88" t="b">
         <v>0</v>
@@ -12915,21 +12948,21 @@
         <v>6542</v>
       </c>
       <c r="T88" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="U88" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>386</v>
-      </c>
-    </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>387</v>
       </c>
       <c r="B89" t="s">
         <v>22</v>
       </c>
       <c r="C89" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D89" t="s">
         <v>204</v>
@@ -12950,7 +12983,7 @@
         <v>9.6032569999999993</v>
       </c>
       <c r="J89" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K89" t="b">
         <v>0</v>
@@ -12980,21 +13013,21 @@
         <v>6362</v>
       </c>
       <c r="T89" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="U89" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>389</v>
-      </c>
-    </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>390</v>
       </c>
       <c r="B90" t="s">
         <v>22</v>
       </c>
       <c r="C90" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D90" t="s">
         <v>209</v>
@@ -13015,7 +13048,7 @@
         <v>10.701789</v>
       </c>
       <c r="J90" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K90" t="b">
         <v>0</v>
@@ -13045,21 +13078,21 @@
         <v>21656</v>
       </c>
       <c r="T90" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="U90" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
         <v>392</v>
-      </c>
-    </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>393</v>
       </c>
       <c r="B91" t="s">
         <v>22</v>
       </c>
       <c r="C91" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D91" t="s">
         <v>214</v>
@@ -13080,7 +13113,7 @@
         <v>10.202757999999999</v>
       </c>
       <c r="J91" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K91" t="b">
         <v>0</v>
@@ -13110,21 +13143,21 @@
         <v>6362</v>
       </c>
       <c r="T91" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="U91" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>395</v>
-      </c>
-    </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>396</v>
       </c>
       <c r="B92" t="s">
         <v>22</v>
       </c>
       <c r="C92" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D92" t="s">
         <v>219</v>
@@ -13145,7 +13178,7 @@
         <v>16.396747000000001</v>
       </c>
       <c r="J92" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K92" t="b">
         <v>0</v>
@@ -13175,21 +13208,21 @@
         <v>4106</v>
       </c>
       <c r="T92" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="U92" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>398</v>
-      </c>
-    </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>399</v>
       </c>
       <c r="B93" t="s">
         <v>22</v>
       </c>
       <c r="C93" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D93" t="s">
         <v>224</v>
@@ -13210,7 +13243,7 @@
         <v>17.187259999999998</v>
       </c>
       <c r="J93" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K93" t="b">
         <v>0</v>
@@ -13240,27 +13273,27 @@
         <v>5002</v>
       </c>
       <c r="T93" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="U93" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>401</v>
-      </c>
-    </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>402</v>
       </c>
       <c r="B94" t="s">
         <v>22</v>
       </c>
       <c r="C94" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D94" t="s">
+        <v>228</v>
+      </c>
+      <c r="E94" t="s">
         <v>229</v>
-      </c>
-      <c r="E94" t="s">
-        <v>230</v>
       </c>
       <c r="F94">
         <v>300</v>
@@ -13275,7 +13308,7 @@
         <v>14.40399</v>
       </c>
       <c r="J94" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K94" t="b">
         <v>0</v>
@@ -13305,27 +13338,27 @@
         <v>4349</v>
       </c>
       <c r="T94" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="U94" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
         <v>404</v>
-      </c>
-    </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>405</v>
       </c>
       <c r="B95" t="s">
         <v>22</v>
       </c>
       <c r="C95" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D95" t="s">
+        <v>233</v>
+      </c>
+      <c r="E95" t="s">
         <v>234</v>
-      </c>
-      <c r="E95" t="s">
-        <v>235</v>
       </c>
       <c r="F95">
         <v>300</v>
@@ -13340,7 +13373,7 @@
         <v>10.570593000000001</v>
       </c>
       <c r="J95" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K95" t="b">
         <v>0</v>
@@ -13370,27 +13403,27 @@
         <v>3503</v>
       </c>
       <c r="T95" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="U95" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>407</v>
-      </c>
-    </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>408</v>
       </c>
       <c r="B96" t="s">
         <v>22</v>
       </c>
       <c r="C96" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D96" t="s">
+        <v>238</v>
+      </c>
+      <c r="E96" t="s">
         <v>239</v>
-      </c>
-      <c r="E96" t="s">
-        <v>240</v>
       </c>
       <c r="F96">
         <v>300</v>
@@ -13405,7 +13438,7 @@
         <v>13.218151000000001</v>
       </c>
       <c r="J96" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K96" t="b">
         <v>0</v>
@@ -13435,27 +13468,27 @@
         <v>4880</v>
       </c>
       <c r="T96" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="U96" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
         <v>410</v>
-      </c>
-    </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>411</v>
       </c>
       <c r="B97" t="s">
         <v>22</v>
       </c>
       <c r="C97" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D97" t="s">
+        <v>243</v>
+      </c>
+      <c r="E97" t="s">
         <v>244</v>
-      </c>
-      <c r="E97" t="s">
-        <v>245</v>
       </c>
       <c r="F97">
         <v>300</v>
@@ -13470,7 +13503,7 @@
         <v>11.683436</v>
       </c>
       <c r="J97" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="K97" t="b">
         <v>0</v>
@@ -13500,27 +13533,27 @@
         <v>3938</v>
       </c>
       <c r="T97" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="U97" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
         <v>413</v>
-      </c>
-    </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>414</v>
       </c>
       <c r="B98" t="s">
         <v>22</v>
       </c>
       <c r="C98" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D98" t="s">
+        <v>248</v>
+      </c>
+      <c r="E98" t="s">
         <v>249</v>
-      </c>
-      <c r="E98" t="s">
-        <v>250</v>
       </c>
       <c r="F98">
         <v>300</v>
@@ -13535,7 +13568,7 @@
         <v>9.2005029999999994</v>
       </c>
       <c r="J98" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="K98" t="b">
         <v>0</v>
@@ -13565,27 +13598,27 @@
         <v>4169</v>
       </c>
       <c r="T98" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="U98" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>416</v>
-      </c>
-    </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>417</v>
       </c>
       <c r="B99" t="s">
         <v>22</v>
       </c>
       <c r="C99" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D99" t="s">
+        <v>253</v>
+      </c>
+      <c r="E99" t="s">
         <v>254</v>
-      </c>
-      <c r="E99" t="s">
-        <v>255</v>
       </c>
       <c r="F99">
         <v>300</v>
@@ -13600,7 +13633,7 @@
         <v>9.6095210000000009</v>
       </c>
       <c r="J99" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="K99" t="b">
         <v>0</v>
@@ -13627,27 +13660,27 @@
         <v>20402</v>
       </c>
       <c r="T99" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="U99" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
         <v>419</v>
-      </c>
-    </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>420</v>
       </c>
       <c r="B100" t="s">
         <v>22</v>
       </c>
       <c r="C100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D100" t="s">
+        <v>258</v>
+      </c>
+      <c r="E100" t="s">
         <v>259</v>
-      </c>
-      <c r="E100" t="s">
-        <v>260</v>
       </c>
       <c r="F100">
         <v>300</v>
@@ -13662,7 +13695,7 @@
         <v>7.281809</v>
       </c>
       <c r="J100" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="K100" t="b">
         <v>0</v>
@@ -13689,27 +13722,27 @@
         <v>20392</v>
       </c>
       <c r="T100" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="U100" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
         <v>422</v>
-      </c>
-    </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>423</v>
       </c>
       <c r="B101" t="s">
         <v>22</v>
       </c>
       <c r="C101" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D101" t="s">
+        <v>263</v>
+      </c>
+      <c r="E101" t="s">
         <v>264</v>
-      </c>
-      <c r="E101" t="s">
-        <v>265</v>
       </c>
       <c r="F101">
         <v>300</v>
@@ -13724,7 +13757,7 @@
         <v>13.656625999999999</v>
       </c>
       <c r="J101" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="K101" t="b">
         <v>0</v>
@@ -13751,27 +13784,27 @@
         <v>20390</v>
       </c>
       <c r="T101" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="U101" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
         <v>425</v>
-      </c>
-    </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>426</v>
       </c>
       <c r="B102" t="s">
         <v>22</v>
       </c>
       <c r="C102" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D102" t="s">
+        <v>268</v>
+      </c>
+      <c r="E102" t="s">
         <v>269</v>
-      </c>
-      <c r="E102" t="s">
-        <v>270</v>
       </c>
       <c r="F102">
         <v>300</v>
@@ -13786,7 +13819,7 @@
         <v>2.8218100000000002</v>
       </c>
       <c r="J102" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="K102" t="b">
         <v>1</v>
@@ -13813,27 +13846,27 @@
         <v>310</v>
       </c>
       <c r="T102" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="U102" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
         <v>428</v>
-      </c>
-    </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>429</v>
       </c>
       <c r="B103" t="s">
         <v>22</v>
       </c>
       <c r="C103" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D103" t="s">
+        <v>273</v>
+      </c>
+      <c r="E103" t="s">
         <v>274</v>
-      </c>
-      <c r="E103" t="s">
-        <v>275</v>
       </c>
       <c r="F103">
         <v>300</v>
@@ -13848,7 +13881,7 @@
         <v>12.741975</v>
       </c>
       <c r="J103" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K103" t="b">
         <v>0</v>
@@ -13875,21 +13908,21 @@
         <v>20398</v>
       </c>
       <c r="T103" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="U103" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>431</v>
-      </c>
-    </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>432</v>
       </c>
       <c r="B104" t="s">
         <v>22</v>
       </c>
       <c r="C104" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D104" t="s">
         <v>24</v>
@@ -13910,7 +13943,7 @@
         <v>32.073269000000003</v>
       </c>
       <c r="J104" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K104" t="b">
         <v>0</v>
@@ -13940,21 +13973,21 @@
         <v>24205</v>
       </c>
       <c r="T104" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="U104" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
         <v>435</v>
-      </c>
-    </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>436</v>
       </c>
       <c r="B105" t="s">
         <v>22</v>
       </c>
       <c r="C105" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D105" t="s">
         <v>29</v>
@@ -13975,7 +14008,7 @@
         <v>15.118432</v>
       </c>
       <c r="J105" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K105" t="b">
         <v>0</v>
@@ -14005,21 +14038,21 @@
         <v>24211</v>
       </c>
       <c r="T105" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="U105" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B106" t="s">
         <v>22</v>
       </c>
       <c r="C106" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D106" t="s">
         <v>34</v>
@@ -14040,7 +14073,7 @@
         <v>43.346972000000001</v>
       </c>
       <c r="J106" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K106" t="b">
         <v>0</v>
@@ -14070,21 +14103,21 @@
         <v>24799</v>
       </c>
       <c r="T106" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="U106" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
         <v>441</v>
-      </c>
-    </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>442</v>
       </c>
       <c r="B107" t="s">
         <v>22</v>
       </c>
       <c r="C107" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D107" t="s">
         <v>39</v>
@@ -14105,7 +14138,7 @@
         <v>12.801574</v>
       </c>
       <c r="J107" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="K107" t="b">
         <v>0</v>
@@ -14135,21 +14168,21 @@
         <v>24223</v>
       </c>
       <c r="T107" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="U107" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
         <v>444</v>
-      </c>
-    </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>445</v>
       </c>
       <c r="B108" t="s">
         <v>22</v>
       </c>
       <c r="C108" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D108" t="s">
         <v>44</v>
@@ -14170,7 +14203,7 @@
         <v>25.230567000000001</v>
       </c>
       <c r="J108" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K108" t="b">
         <v>0</v>
@@ -14200,21 +14233,21 @@
         <v>24217</v>
       </c>
       <c r="T108" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="U108" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
         <v>447</v>
-      </c>
-    </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>448</v>
       </c>
       <c r="B109" t="s">
         <v>22</v>
       </c>
       <c r="C109" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D109" t="s">
         <v>49</v>
@@ -14235,7 +14268,7 @@
         <v>15.644261999999999</v>
       </c>
       <c r="J109" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="K109" t="b">
         <v>0</v>
@@ -14265,21 +14298,21 @@
         <v>24268</v>
       </c>
       <c r="T109" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="U109" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
         <v>450</v>
-      </c>
-    </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>451</v>
       </c>
       <c r="B110" t="s">
         <v>22</v>
       </c>
       <c r="C110" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D110" t="s">
         <v>54</v>
@@ -14300,7 +14333,7 @@
         <v>9.4007240000000003</v>
       </c>
       <c r="J110" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K110" t="b">
         <v>0</v>
@@ -14330,21 +14363,21 @@
         <v>24301</v>
       </c>
       <c r="T110" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="U110" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
         <v>453</v>
-      </c>
-    </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>454</v>
       </c>
       <c r="B111" t="s">
         <v>22</v>
       </c>
       <c r="C111" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D111" t="s">
         <v>59</v>
@@ -14365,7 +14398,7 @@
         <v>15.929788</v>
       </c>
       <c r="J111" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K111" t="b">
         <v>0</v>
@@ -14395,21 +14428,21 @@
         <v>24346</v>
       </c>
       <c r="T111" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="U111" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>456</v>
-      </c>
-    </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>457</v>
       </c>
       <c r="B112" t="s">
         <v>22</v>
       </c>
       <c r="C112" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D112" t="s">
         <v>64</v>
@@ -14430,7 +14463,7 @@
         <v>8.5176580000000008</v>
       </c>
       <c r="J112" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K112" t="b">
         <v>0</v>
@@ -14460,21 +14493,21 @@
         <v>24623</v>
       </c>
       <c r="T112" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="U112" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
         <v>459</v>
-      </c>
-    </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>460</v>
       </c>
       <c r="B113" t="s">
         <v>22</v>
       </c>
       <c r="C113" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D113" t="s">
         <v>69</v>
@@ -14495,7 +14528,7 @@
         <v>17.655235000000001</v>
       </c>
       <c r="J113" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K113" t="b">
         <v>0</v>
@@ -14525,21 +14558,21 @@
         <v>25008</v>
       </c>
       <c r="T113" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="U113" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
         <v>462</v>
-      </c>
-    </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>463</v>
       </c>
       <c r="B114" t="s">
         <v>22</v>
       </c>
       <c r="C114" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D114" t="s">
         <v>74</v>
@@ -14560,7 +14593,7 @@
         <v>15.031040000000001</v>
       </c>
       <c r="J114" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K114" t="b">
         <v>0</v>
@@ -14590,21 +14623,21 @@
         <v>26415</v>
       </c>
       <c r="T114" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="U114" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
         <v>465</v>
-      </c>
-    </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>466</v>
       </c>
       <c r="B115" t="s">
         <v>22</v>
       </c>
       <c r="C115" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D115" t="s">
         <v>79</v>
@@ -14625,7 +14658,7 @@
         <v>13.257707</v>
       </c>
       <c r="J115" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K115" t="b">
         <v>0</v>
@@ -14655,21 +14688,21 @@
         <v>26412</v>
       </c>
       <c r="T115" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="U115" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="116" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
         <v>468</v>
-      </c>
-    </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>469</v>
       </c>
       <c r="B116" t="s">
         <v>22</v>
       </c>
       <c r="C116" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D116" t="s">
         <v>84</v>
@@ -14690,7 +14723,7 @@
         <v>18.474086</v>
       </c>
       <c r="J116" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K116" t="b">
         <v>0</v>
@@ -14720,21 +14753,21 @@
         <v>26905</v>
       </c>
       <c r="T116" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="U116" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="117" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
         <v>471</v>
-      </c>
-    </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>472</v>
       </c>
       <c r="B117" t="s">
         <v>22</v>
       </c>
       <c r="C117" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D117" t="s">
         <v>89</v>
@@ -14755,7 +14788,7 @@
         <v>14.742858999999999</v>
       </c>
       <c r="J117" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K117" t="b">
         <v>0</v>
@@ -14785,21 +14818,21 @@
         <v>26418</v>
       </c>
       <c r="T117" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="U117" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B118" t="s">
         <v>22</v>
       </c>
       <c r="C118" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D118" t="s">
         <v>94</v>
@@ -14820,7 +14853,7 @@
         <v>11.045552000000001</v>
       </c>
       <c r="J118" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="K118" t="b">
         <v>0</v>
@@ -14850,21 +14883,21 @@
         <v>26484</v>
       </c>
       <c r="T118" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="U118" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
         <v>477</v>
-      </c>
-    </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>478</v>
       </c>
       <c r="B119" t="s">
         <v>22</v>
       </c>
       <c r="C119" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D119" t="s">
         <v>99</v>
@@ -14885,7 +14918,7 @@
         <v>8.3961229999999993</v>
       </c>
       <c r="J119" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K119" t="b">
         <v>0</v>
@@ -14915,21 +14948,21 @@
         <v>26421</v>
       </c>
       <c r="T119" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="U119" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="120" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
         <v>480</v>
-      </c>
-    </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>481</v>
       </c>
       <c r="B120" t="s">
         <v>22</v>
       </c>
       <c r="C120" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D120" t="s">
         <v>104</v>
@@ -14950,7 +14983,7 @@
         <v>9.9906220000000001</v>
       </c>
       <c r="J120" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K120" t="b">
         <v>0</v>
@@ -14980,21 +15013,21 @@
         <v>26443</v>
       </c>
       <c r="T120" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="U120" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="121" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
         <v>483</v>
-      </c>
-    </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>484</v>
       </c>
       <c r="B121" t="s">
         <v>22</v>
       </c>
       <c r="C121" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D121" t="s">
         <v>109</v>
@@ -15015,7 +15048,7 @@
         <v>8.5688209999999998</v>
       </c>
       <c r="J121" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K121" t="b">
         <v>0</v>
@@ -15045,21 +15078,21 @@
         <v>26442</v>
       </c>
       <c r="T121" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="U121" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B122" t="s">
         <v>22</v>
       </c>
       <c r="C122" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D122" t="s">
         <v>114</v>
@@ -15080,7 +15113,7 @@
         <v>7.9413460000000002</v>
       </c>
       <c r="J122" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="K122" t="b">
         <v>0</v>
@@ -15110,21 +15143,21 @@
         <v>26423</v>
       </c>
       <c r="T122" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="U122" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
         <v>489</v>
-      </c>
-    </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>490</v>
       </c>
       <c r="B123" t="s">
         <v>22</v>
       </c>
       <c r="C123" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D123" t="s">
         <v>119</v>
@@ -15145,7 +15178,7 @@
         <v>14.751744</v>
       </c>
       <c r="J123" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K123" t="b">
         <v>0</v>
@@ -15175,21 +15208,21 @@
         <v>20756</v>
       </c>
       <c r="T123" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="U123" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B124" t="s">
         <v>22</v>
       </c>
       <c r="C124" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D124" t="s">
         <v>124</v>
@@ -15210,7 +15243,7 @@
         <v>16.118891999999999</v>
       </c>
       <c r="J124" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="K124" t="b">
         <v>0</v>
@@ -15240,21 +15273,21 @@
         <v>20760</v>
       </c>
       <c r="T124" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="U124" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B125" t="s">
         <v>22</v>
       </c>
       <c r="C125" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D125" t="s">
         <v>129</v>
@@ -15275,7 +15308,7 @@
         <v>13.947672000000001</v>
       </c>
       <c r="J125" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K125" t="b">
         <v>0</v>
@@ -15305,21 +15338,21 @@
         <v>20768</v>
       </c>
       <c r="T125" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="U125" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
         <v>498</v>
-      </c>
-    </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>499</v>
       </c>
       <c r="B126" t="s">
         <v>22</v>
       </c>
       <c r="C126" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D126" t="s">
         <v>134</v>
@@ -15340,7 +15373,7 @@
         <v>14.938355</v>
       </c>
       <c r="J126" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K126" t="b">
         <v>0</v>
@@ -15370,21 +15403,21 @@
         <v>21033</v>
       </c>
       <c r="T126" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="U126" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
         <v>501</v>
-      </c>
-    </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>502</v>
       </c>
       <c r="B127" t="s">
         <v>22</v>
       </c>
       <c r="C127" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D127" t="s">
         <v>139</v>
@@ -15405,7 +15438,7 @@
         <v>14.913812999999999</v>
       </c>
       <c r="J127" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="K127" t="b">
         <v>0</v>
@@ -15435,21 +15468,21 @@
         <v>20911</v>
       </c>
       <c r="T127" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="U127" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
         <v>504</v>
-      </c>
-    </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>505</v>
       </c>
       <c r="B128" t="s">
         <v>22</v>
       </c>
       <c r="C128" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D128" t="s">
         <v>144</v>
@@ -15470,7 +15503,7 @@
         <v>11.013956</v>
       </c>
       <c r="J128" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="K128" t="b">
         <v>0</v>
@@ -15500,21 +15533,21 @@
         <v>21034</v>
       </c>
       <c r="T128" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="U128" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
         <v>507</v>
-      </c>
-    </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>508</v>
       </c>
       <c r="B129" t="s">
         <v>22</v>
       </c>
       <c r="C129" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D129" t="s">
         <v>149</v>
@@ -15535,7 +15568,7 @@
         <v>11.691692</v>
       </c>
       <c r="J129" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="K129" t="b">
         <v>0</v>
@@ -15565,21 +15598,21 @@
         <v>20813</v>
       </c>
       <c r="T129" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="U129" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="130" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
         <v>510</v>
-      </c>
-    </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>511</v>
       </c>
       <c r="B130" t="s">
         <v>22</v>
       </c>
       <c r="C130" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D130" t="s">
         <v>154</v>
@@ -15600,7 +15633,7 @@
         <v>12.036652</v>
       </c>
       <c r="J130" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K130" t="b">
         <v>0</v>
@@ -15630,21 +15663,21 @@
         <v>20738</v>
       </c>
       <c r="T130" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="U130" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="131" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
         <v>513</v>
-      </c>
-    </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>514</v>
       </c>
       <c r="B131" t="s">
         <v>22</v>
       </c>
       <c r="C131" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D131" t="s">
         <v>159</v>
@@ -15665,7 +15698,7 @@
         <v>12.258293</v>
       </c>
       <c r="J131" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K131" t="b">
         <v>0</v>
@@ -15695,21 +15728,21 @@
         <v>20735</v>
       </c>
       <c r="T131" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="U131" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B132" t="s">
         <v>22</v>
       </c>
       <c r="C132" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D132" t="s">
         <v>164</v>
@@ -15730,7 +15763,7 @@
         <v>11.989172999999999</v>
       </c>
       <c r="J132" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="K132" t="b">
         <v>0</v>
@@ -15760,21 +15793,21 @@
         <v>20734</v>
       </c>
       <c r="T132" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="U132" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="133" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
         <v>519</v>
-      </c>
-    </row>
-    <row r="133" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>520</v>
       </c>
       <c r="B133" t="s">
         <v>22</v>
       </c>
       <c r="C133" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D133" t="s">
         <v>169</v>
@@ -15795,7 +15828,7 @@
         <v>14.421938000000001</v>
       </c>
       <c r="J133" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K133" t="b">
         <v>0</v>
@@ -15825,21 +15858,21 @@
         <v>20231</v>
       </c>
       <c r="T133" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="U133" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B134" t="s">
         <v>22</v>
       </c>
       <c r="C134" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D134" t="s">
         <v>174</v>
@@ -15860,7 +15893,7 @@
         <v>18.703762999999999</v>
       </c>
       <c r="J134" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K134" t="b">
         <v>0</v>
@@ -15890,21 +15923,21 @@
         <v>20638</v>
       </c>
       <c r="T134" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="U134" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="135" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
         <v>525</v>
-      </c>
-    </row>
-    <row r="135" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>526</v>
       </c>
       <c r="B135" t="s">
         <v>22</v>
       </c>
       <c r="C135" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D135" t="s">
         <v>179</v>
@@ -15925,7 +15958,7 @@
         <v>15.746623</v>
       </c>
       <c r="J135" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="K135" t="b">
         <v>0</v>
@@ -15955,21 +15988,21 @@
         <v>20220</v>
       </c>
       <c r="T135" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="U135" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B136" t="s">
         <v>22</v>
       </c>
       <c r="C136" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D136" t="s">
         <v>184</v>
@@ -15990,7 +16023,7 @@
         <v>12.352067</v>
       </c>
       <c r="J136" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K136" t="b">
         <v>0</v>
@@ -16020,21 +16053,21 @@
         <v>20468</v>
       </c>
       <c r="T136" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="U136" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="137" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
         <v>531</v>
-      </c>
-    </row>
-    <row r="137" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>532</v>
       </c>
       <c r="B137" t="s">
         <v>22</v>
       </c>
       <c r="C137" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D137" t="s">
         <v>189</v>
@@ -16055,7 +16088,7 @@
         <v>19.833335000000002</v>
       </c>
       <c r="J137" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="K137" t="b">
         <v>0</v>
@@ -16085,21 +16118,21 @@
         <v>20208</v>
       </c>
       <c r="T137" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="U137" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="138" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
         <v>534</v>
-      </c>
-    </row>
-    <row r="138" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>535</v>
       </c>
       <c r="B138" t="s">
         <v>22</v>
       </c>
       <c r="C138" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D138" t="s">
         <v>194</v>
@@ -16120,7 +16153,7 @@
         <v>12.777639000000001</v>
       </c>
       <c r="J138" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="K138" t="b">
         <v>0</v>
@@ -16150,21 +16183,21 @@
         <v>20196</v>
       </c>
       <c r="T138" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="U138" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="139" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
         <v>537</v>
-      </c>
-    </row>
-    <row r="139" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>538</v>
       </c>
       <c r="B139" t="s">
         <v>22</v>
       </c>
       <c r="C139" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D139" t="s">
         <v>199</v>
@@ -16185,7 +16218,7 @@
         <v>15.930611000000001</v>
       </c>
       <c r="J139" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="K139" t="b">
         <v>0</v>
@@ -16215,21 +16248,21 @@
         <v>20266</v>
       </c>
       <c r="T139" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="U139" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="140" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
         <v>540</v>
-      </c>
-    </row>
-    <row r="140" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>541</v>
       </c>
       <c r="B140" t="s">
         <v>22</v>
       </c>
       <c r="C140" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D140" t="s">
         <v>204</v>
@@ -16250,7 +16283,7 @@
         <v>15.881968000000001</v>
       </c>
       <c r="J140" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="K140" t="b">
         <v>0</v>
@@ -16280,21 +16313,21 @@
         <v>20206</v>
       </c>
       <c r="T140" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="U140" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="141" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
         <v>543</v>
-      </c>
-    </row>
-    <row r="141" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>544</v>
       </c>
       <c r="B141" t="s">
         <v>22</v>
       </c>
       <c r="C141" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D141" t="s">
         <v>209</v>
@@ -16315,7 +16348,7 @@
         <v>8.6481410000000007</v>
       </c>
       <c r="J141" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="K141" t="b">
         <v>0</v>
@@ -16345,21 +16378,21 @@
         <v>20223</v>
       </c>
       <c r="T141" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="U141" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="142" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
         <v>546</v>
-      </c>
-    </row>
-    <row r="142" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>547</v>
       </c>
       <c r="B142" t="s">
         <v>22</v>
       </c>
       <c r="C142" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D142" t="s">
         <v>214</v>
@@ -16380,7 +16413,7 @@
         <v>16.807977999999999</v>
       </c>
       <c r="J142" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="K142" t="b">
         <v>0</v>
@@ -16410,21 +16443,21 @@
         <v>20206</v>
       </c>
       <c r="T142" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="U142" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="143" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
         <v>549</v>
-      </c>
-    </row>
-    <row r="143" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>550</v>
       </c>
       <c r="B143" t="s">
         <v>22</v>
       </c>
       <c r="C143" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D143" t="s">
         <v>219</v>
@@ -16445,7 +16478,7 @@
         <v>15.630621</v>
       </c>
       <c r="J143" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="K143" t="b">
         <v>0</v>
@@ -16475,21 +16508,21 @@
         <v>20522</v>
       </c>
       <c r="T143" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="U143" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="144" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
         <v>552</v>
-      </c>
-    </row>
-    <row r="144" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>553</v>
       </c>
       <c r="B144" t="s">
         <v>22</v>
       </c>
       <c r="C144" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D144" t="s">
         <v>224</v>
@@ -16510,7 +16543,7 @@
         <v>13.338291999999999</v>
       </c>
       <c r="J144" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K144" t="b">
         <v>0</v>
@@ -16540,27 +16573,27 @@
         <v>20820</v>
       </c>
       <c r="T144" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="U144" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="145" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
         <v>555</v>
-      </c>
-    </row>
-    <row r="145" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>556</v>
       </c>
       <c r="B145" t="s">
         <v>22</v>
       </c>
       <c r="C145" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D145" t="s">
+        <v>228</v>
+      </c>
+      <c r="E145" t="s">
         <v>229</v>
-      </c>
-      <c r="E145" t="s">
-        <v>230</v>
       </c>
       <c r="F145">
         <v>300</v>
@@ -16575,7 +16608,7 @@
         <v>13.819069000000001</v>
       </c>
       <c r="J145" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="K145" t="b">
         <v>0</v>
@@ -16605,27 +16638,27 @@
         <v>20603</v>
       </c>
       <c r="T145" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="U145" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="146" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
         <v>558</v>
-      </c>
-    </row>
-    <row r="146" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>559</v>
       </c>
       <c r="B146" t="s">
         <v>22</v>
       </c>
       <c r="C146" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D146" t="s">
+        <v>233</v>
+      </c>
+      <c r="E146" t="s">
         <v>234</v>
-      </c>
-      <c r="E146" t="s">
-        <v>235</v>
       </c>
       <c r="F146">
         <v>300</v>
@@ -16640,7 +16673,7 @@
         <v>11.326670999999999</v>
       </c>
       <c r="J146" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="K146" t="b">
         <v>0</v>
@@ -16670,27 +16703,27 @@
         <v>20321</v>
       </c>
       <c r="T146" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="U146" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="147" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
         <v>561</v>
-      </c>
-    </row>
-    <row r="147" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>562</v>
       </c>
       <c r="B147" t="s">
         <v>22</v>
       </c>
       <c r="C147" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D147" t="s">
+        <v>238</v>
+      </c>
+      <c r="E147" t="s">
         <v>239</v>
-      </c>
-      <c r="E147" t="s">
-        <v>240</v>
       </c>
       <c r="F147">
         <v>300</v>
@@ -16705,7 +16738,7 @@
         <v>23.992815</v>
       </c>
       <c r="J147" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="K147" t="b">
         <v>0</v>
@@ -16735,27 +16768,27 @@
         <v>20780</v>
       </c>
       <c r="T147" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="U147" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="148" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
         <v>564</v>
-      </c>
-    </row>
-    <row r="148" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>565</v>
       </c>
       <c r="B148" t="s">
         <v>22</v>
       </c>
       <c r="C148" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D148" t="s">
+        <v>243</v>
+      </c>
+      <c r="E148" t="s">
         <v>244</v>
-      </c>
-      <c r="E148" t="s">
-        <v>245</v>
       </c>
       <c r="F148">
         <v>300</v>
@@ -16770,7 +16803,7 @@
         <v>9.6451159999999998</v>
       </c>
       <c r="J148" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="K148" t="b">
         <v>0</v>
@@ -16800,27 +16833,27 @@
         <v>20466</v>
       </c>
       <c r="T148" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="U148" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="149" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
         <v>567</v>
-      </c>
-    </row>
-    <row r="149" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>568</v>
       </c>
       <c r="B149" t="s">
         <v>22</v>
       </c>
       <c r="C149" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D149" t="s">
+        <v>248</v>
+      </c>
+      <c r="E149" t="s">
         <v>249</v>
-      </c>
-      <c r="E149" t="s">
-        <v>250</v>
       </c>
       <c r="F149">
         <v>300</v>
@@ -16835,7 +16868,7 @@
         <v>19.310569999999998</v>
       </c>
       <c r="J149" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="K149" t="b">
         <v>0</v>
@@ -16865,27 +16898,27 @@
         <v>20543</v>
       </c>
       <c r="T149" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="U149" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="150" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
         <v>570</v>
-      </c>
-    </row>
-    <row r="150" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>571</v>
       </c>
       <c r="B150" t="s">
         <v>22</v>
       </c>
       <c r="C150" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D150" t="s">
+        <v>253</v>
+      </c>
+      <c r="E150" t="s">
         <v>254</v>
-      </c>
-      <c r="E150" t="s">
-        <v>255</v>
       </c>
       <c r="F150">
         <v>300</v>
@@ -16900,7 +16933,7 @@
         <v>23.142779999999998</v>
       </c>
       <c r="J150" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="K150" t="b">
         <v>0</v>
@@ -16927,27 +16960,27 @@
         <v>20195</v>
       </c>
       <c r="T150" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="U150" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="151" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
         <v>573</v>
-      </c>
-    </row>
-    <row r="151" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>574</v>
       </c>
       <c r="B151" t="s">
         <v>22</v>
       </c>
       <c r="C151" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D151" t="s">
+        <v>258</v>
+      </c>
+      <c r="E151" t="s">
         <v>259</v>
-      </c>
-      <c r="E151" t="s">
-        <v>260</v>
       </c>
       <c r="F151">
         <v>300</v>
@@ -16962,7 +16995,7 @@
         <v>10.174884</v>
       </c>
       <c r="J151" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="K151" t="b">
         <v>0</v>
@@ -16989,27 +17022,27 @@
         <v>20190</v>
       </c>
       <c r="T151" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="U151" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="152" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
         <v>576</v>
-      </c>
-    </row>
-    <row r="152" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>577</v>
       </c>
       <c r="B152" t="s">
         <v>22</v>
       </c>
       <c r="C152" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D152" t="s">
+        <v>263</v>
+      </c>
+      <c r="E152" t="s">
         <v>264</v>
-      </c>
-      <c r="E152" t="s">
-        <v>265</v>
       </c>
       <c r="F152">
         <v>300</v>
@@ -17024,7 +17057,7 @@
         <v>12.483865</v>
       </c>
       <c r="J152" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K152" t="b">
         <v>0</v>
@@ -17051,27 +17084,27 @@
         <v>20189</v>
       </c>
       <c r="T152" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="U152" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="153" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
         <v>579</v>
-      </c>
-    </row>
-    <row r="153" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>580</v>
       </c>
       <c r="B153" t="s">
         <v>22</v>
       </c>
       <c r="C153" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D153" t="s">
+        <v>268</v>
+      </c>
+      <c r="E153" t="s">
         <v>269</v>
-      </c>
-      <c r="E153" t="s">
-        <v>270</v>
       </c>
       <c r="F153">
         <v>300</v>
@@ -17086,7 +17119,7 @@
         <v>9.2682169999999999</v>
       </c>
       <c r="J153" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="K153" t="b">
         <v>0</v>
@@ -17113,27 +17146,27 @@
         <v>20186</v>
       </c>
       <c r="T153" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="U153" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="154" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
         <v>582</v>
-      </c>
-    </row>
-    <row r="154" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>583</v>
       </c>
       <c r="B154" t="s">
         <v>22</v>
       </c>
       <c r="C154" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D154" t="s">
+        <v>273</v>
+      </c>
+      <c r="E154" t="s">
         <v>274</v>
-      </c>
-      <c r="E154" t="s">
-        <v>275</v>
       </c>
       <c r="F154">
         <v>300</v>
@@ -17148,7 +17181,7 @@
         <v>13.229730999999999</v>
       </c>
       <c r="J154" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="K154" t="b">
         <v>0</v>
@@ -17175,13 +17208,20 @@
         <v>20193</v>
       </c>
       <c r="T154" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="U154" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:U154" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="11">
+      <filters>
+        <filter val="0"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>